--- a/data/maintenance_log.xlsx
+++ b/data/maintenance_log.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -446,28 +446,38 @@
           <t>الكود</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>حالة الدعم الفني</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>نوع العمل</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>الوصف</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>أيام التوقف</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>التكلفة</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Supported/Active,Limited Supported,EOL,Obsolete"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
